--- a/output/yearly_population_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_25_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6974</v>
+        <v>5686</v>
       </c>
       <c r="C2" t="n">
-        <v>9891</v>
+        <v>5228</v>
       </c>
       <c r="D2" t="n">
-        <v>24767</v>
+        <v>25667</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4639</v>
+        <v>3865</v>
       </c>
       <c r="C3" t="n">
-        <v>4535</v>
+        <v>4487</v>
       </c>
       <c r="D3" t="n">
-        <v>14951</v>
+        <v>12775</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3503</v>
+        <v>2986</v>
       </c>
       <c r="C4" t="n">
-        <v>4317</v>
+        <v>5437</v>
       </c>
       <c r="D4" t="n">
-        <v>8161</v>
+        <v>5392</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2209</v>
+        <v>1953</v>
       </c>
       <c r="C5" t="n">
-        <v>3901</v>
+        <v>4822</v>
       </c>
       <c r="D5" t="n">
-        <v>3442</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1209</v>
+        <v>1135</v>
       </c>
       <c r="C6" t="n">
-        <v>2685</v>
+        <v>3196</v>
       </c>
       <c r="D6" t="n">
-        <v>1395</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>560</v>
+        <v>531</v>
       </c>
       <c r="C7" t="n">
-        <v>1383</v>
+        <v>1792</v>
       </c>
       <c r="D7" t="n">
-        <v>703</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="C8" t="n">
-        <v>545</v>
+        <v>826</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>374</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -926,7 +926,7 @@
         <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8409</v>
+        <v>6773</v>
       </c>
       <c r="C2" t="n">
-        <v>16452</v>
+        <v>7756</v>
       </c>
       <c r="D2" t="n">
-        <v>20418</v>
+        <v>20286</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4635</v>
+        <v>3820</v>
       </c>
       <c r="C3" t="n">
-        <v>6133</v>
+        <v>4244</v>
       </c>
       <c r="D3" t="n">
-        <v>15281</v>
+        <v>13669</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3420</v>
+        <v>2884</v>
       </c>
       <c r="C4" t="n">
-        <v>4290</v>
+        <v>4815</v>
       </c>
       <c r="D4" t="n">
-        <v>8942</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2468</v>
+        <v>2143</v>
       </c>
       <c r="C5" t="n">
-        <v>4015</v>
+        <v>5010</v>
       </c>
       <c r="D5" t="n">
-        <v>4107</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1488</v>
+        <v>1354</v>
       </c>
       <c r="C6" t="n">
-        <v>3181</v>
+        <v>3867</v>
       </c>
       <c r="D6" t="n">
-        <v>1677</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>750</v>
+        <v>707</v>
       </c>
       <c r="C7" t="n">
-        <v>1969</v>
+        <v>2424</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="C8" t="n">
-        <v>900</v>
+        <v>1234</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>382</v>
+        <v>564</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1237,7 +1237,7 @@
         <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8934</v>
+        <v>7676</v>
       </c>
       <c r="C2" t="n">
-        <v>15618</v>
+        <v>6101</v>
       </c>
       <c r="D2" t="n">
-        <v>28942</v>
+        <v>24118</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5004</v>
+        <v>4098</v>
       </c>
       <c r="C3" t="n">
-        <v>9233</v>
+        <v>5054</v>
       </c>
       <c r="D3" t="n">
-        <v>14936</v>
+        <v>13619</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3336</v>
+        <v>2817</v>
       </c>
       <c r="C4" t="n">
-        <v>4973</v>
+        <v>4416</v>
       </c>
       <c r="D4" t="n">
-        <v>9643</v>
+        <v>7306</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2537</v>
+        <v>2176</v>
       </c>
       <c r="C5" t="n">
-        <v>4050</v>
+        <v>4821</v>
       </c>
       <c r="D5" t="n">
-        <v>4638</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1714</v>
+        <v>1526</v>
       </c>
       <c r="C6" t="n">
-        <v>3465</v>
+        <v>4266</v>
       </c>
       <c r="D6" t="n">
-        <v>2004</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>938</v>
+        <v>869</v>
       </c>
       <c r="C7" t="n">
-        <v>2447</v>
+        <v>2993</v>
       </c>
       <c r="D7" t="n">
-        <v>907</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="C8" t="n">
-        <v>1329</v>
+        <v>1711</v>
       </c>
       <c r="D8" t="n">
-        <v>508</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C9" t="n">
-        <v>576</v>
+        <v>814</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>283</v>
+        <v>382</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1590,7 +1590,7 @@
         <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8225</v>
+        <v>7024</v>
       </c>
       <c r="C2" t="n">
-        <v>10620</v>
+        <v>4099</v>
       </c>
       <c r="D2" t="n">
-        <v>23727</v>
+        <v>19817</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6039</v>
+        <v>5018</v>
       </c>
       <c r="C3" t="n">
-        <v>12742</v>
+        <v>7413</v>
       </c>
       <c r="D3" t="n">
-        <v>16634</v>
+        <v>14725</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2344</v>
+        <v>2010</v>
       </c>
       <c r="C4" t="n">
-        <v>6656</v>
+        <v>7086</v>
       </c>
       <c r="D4" t="n">
-        <v>9593</v>
+        <v>6883</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1583</v>
+        <v>1410</v>
       </c>
       <c r="C5" t="n">
-        <v>3395</v>
+        <v>4180</v>
       </c>
       <c r="D5" t="n">
-        <v>3210</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>866</v>
+        <v>802</v>
       </c>
       <c r="C6" t="n">
-        <v>2398</v>
+        <v>2933</v>
       </c>
       <c r="D6" t="n">
-        <v>888</v>
+        <v>723</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="C7" t="n">
-        <v>1302</v>
+        <v>1676</v>
       </c>
       <c r="D7" t="n">
-        <v>497</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C8" t="n">
-        <v>564</v>
+        <v>797</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>374</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1887,7 +1887,7 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5124</v>
+        <v>4351</v>
       </c>
       <c r="C2" t="n">
-        <v>4342</v>
+        <v>3263</v>
       </c>
       <c r="D2" t="n">
-        <v>16723</v>
+        <v>13941</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6042</v>
+        <v>5082</v>
       </c>
       <c r="C3" t="n">
-        <v>10656</v>
+        <v>5334</v>
       </c>
       <c r="D3" t="n">
-        <v>16640</v>
+        <v>14569</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3298</v>
+        <v>2763</v>
       </c>
       <c r="C4" t="n">
-        <v>9636</v>
+        <v>7296</v>
       </c>
       <c r="D4" t="n">
-        <v>10567</v>
+        <v>8010</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1757</v>
+        <v>1565</v>
       </c>
       <c r="C5" t="n">
-        <v>4833</v>
+        <v>5521</v>
       </c>
       <c r="D5" t="n">
-        <v>3970</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1045</v>
+        <v>961</v>
       </c>
       <c r="C6" t="n">
-        <v>2865</v>
+        <v>3554</v>
       </c>
       <c r="D6" t="n">
-        <v>1126</v>
+        <v>871</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>1717</v>
+        <v>2151</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>766</v>
+        <v>1071</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>428</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5657</v>
+        <v>5086</v>
       </c>
       <c r="C2" t="n">
-        <v>10906</v>
+        <v>4490</v>
       </c>
       <c r="D2" t="n">
-        <v>25017</v>
+        <v>17927</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4748</v>
+        <v>3999</v>
       </c>
       <c r="C3" t="n">
-        <v>6818</v>
+        <v>3841</v>
       </c>
       <c r="D3" t="n">
-        <v>15666</v>
+        <v>13476</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3876</v>
+        <v>3274</v>
       </c>
       <c r="C4" t="n">
-        <v>9934</v>
+        <v>6164</v>
       </c>
       <c r="D4" t="n">
-        <v>11236</v>
+        <v>8899</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2134</v>
+        <v>1852</v>
       </c>
       <c r="C5" t="n">
-        <v>6991</v>
+        <v>6258</v>
       </c>
       <c r="D5" t="n">
-        <v>4862</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1231</v>
+        <v>1129</v>
       </c>
       <c r="C6" t="n">
-        <v>3752</v>
+        <v>4459</v>
       </c>
       <c r="D6" t="n">
-        <v>1520</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>565</v>
+        <v>520</v>
       </c>
       <c r="C7" t="n">
-        <v>2228</v>
+        <v>2789</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>1155</v>
+        <v>1525</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>492</v>
+        <v>677</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2579,7 +2579,7 @@
         <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3375</v>
+        <v>2988</v>
       </c>
       <c r="C2" t="n">
-        <v>5091</v>
+        <v>2091</v>
       </c>
       <c r="D2" t="n">
-        <v>17435</v>
+        <v>12364</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4831</v>
+        <v>4116</v>
       </c>
       <c r="C3" t="n">
-        <v>7984</v>
+        <v>3904</v>
       </c>
       <c r="D3" t="n">
-        <v>16287</v>
+        <v>13651</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4222</v>
+        <v>3625</v>
       </c>
       <c r="C4" t="n">
-        <v>9663</v>
+        <v>5883</v>
       </c>
       <c r="D4" t="n">
-        <v>11863</v>
+        <v>9495</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2214</v>
+        <v>1959</v>
       </c>
       <c r="C5" t="n">
-        <v>8694</v>
+        <v>7122</v>
       </c>
       <c r="D5" t="n">
-        <v>5108</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1022</v>
+        <v>949</v>
       </c>
       <c r="C6" t="n">
-        <v>4512</v>
+        <v>5462</v>
       </c>
       <c r="D6" t="n">
-        <v>1477</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>2243</v>
+        <v>2902</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>833</v>
+        <v>1141</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2876,7 +2876,7 @@
         <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
+        <v>3960</v>
       </c>
       <c r="C2" t="n">
-        <v>6694</v>
+        <v>2475</v>
       </c>
       <c r="D2" t="n">
-        <v>14136</v>
+        <v>15798</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3617</v>
+        <v>3072</v>
       </c>
       <c r="C3" t="n">
-        <v>5945</v>
+        <v>2706</v>
       </c>
       <c r="D3" t="n">
-        <v>15504</v>
+        <v>12558</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3943</v>
+        <v>3383</v>
       </c>
       <c r="C4" t="n">
-        <v>8764</v>
+        <v>4848</v>
       </c>
       <c r="D4" t="n">
-        <v>12181</v>
+        <v>9884</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2670</v>
+        <v>2355</v>
       </c>
       <c r="C5" t="n">
-        <v>9024</v>
+        <v>6471</v>
       </c>
       <c r="D5" t="n">
-        <v>5925</v>
+        <v>4561</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1323</v>
+        <v>1228</v>
       </c>
       <c r="C6" t="n">
-        <v>6241</v>
+        <v>6181</v>
       </c>
       <c r="D6" t="n">
-        <v>1945</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="C7" t="n">
-        <v>3175</v>
+        <v>4011</v>
       </c>
       <c r="D7" t="n">
-        <v>721</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1346</v>
+        <v>1818</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>439</v>
+        <v>587</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3449</v>
+        <v>2800</v>
       </c>
       <c r="C2" t="n">
-        <v>3584</v>
+        <v>2246</v>
       </c>
       <c r="D2" t="n">
-        <v>10697</v>
+        <v>12549</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3485</v>
+        <v>2951</v>
       </c>
       <c r="C3" t="n">
-        <v>5723</v>
+        <v>2365</v>
       </c>
       <c r="D3" t="n">
-        <v>14645</v>
+        <v>12263</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3514</v>
+        <v>3028</v>
       </c>
       <c r="C4" t="n">
-        <v>7640</v>
+        <v>3982</v>
       </c>
       <c r="D4" t="n">
-        <v>12342</v>
+        <v>10037</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2910</v>
+        <v>2563</v>
       </c>
       <c r="C5" t="n">
-        <v>9090</v>
+        <v>5977</v>
       </c>
       <c r="D5" t="n">
-        <v>6462</v>
+        <v>5123</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1550</v>
+        <v>1440</v>
       </c>
       <c r="C6" t="n">
-        <v>7333</v>
+        <v>6532</v>
       </c>
       <c r="D6" t="n">
-        <v>2322</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="C7" t="n">
-        <v>4112</v>
+        <v>4837</v>
       </c>
       <c r="D7" t="n">
-        <v>806</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1754</v>
+        <v>2360</v>
       </c>
       <c r="D8" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>507</v>
+        <v>709</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4428</v>
+        <v>4878</v>
       </c>
       <c r="C2" t="n">
-        <v>13971</v>
+        <v>6858</v>
       </c>
       <c r="D2" t="n">
-        <v>9941</v>
+        <v>13355</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2923</v>
+        <v>2435</v>
       </c>
       <c r="C3" t="n">
-        <v>4393</v>
+        <v>2052</v>
       </c>
       <c r="D3" t="n">
-        <v>13233</v>
+        <v>11495</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3045</v>
+        <v>2607</v>
       </c>
       <c r="C4" t="n">
-        <v>6689</v>
+        <v>3185</v>
       </c>
       <c r="D4" t="n">
-        <v>12298</v>
+        <v>10073</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2870</v>
+        <v>2489</v>
       </c>
       <c r="C5" t="n">
-        <v>8330</v>
+        <v>5009</v>
       </c>
       <c r="D5" t="n">
-        <v>7055</v>
+        <v>5674</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1852</v>
+        <v>1712</v>
       </c>
       <c r="C6" t="n">
-        <v>7930</v>
+        <v>6250</v>
       </c>
       <c r="D6" t="n">
-        <v>2808</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="C7" t="n">
-        <v>5278</v>
+        <v>5546</v>
       </c>
       <c r="D7" t="n">
-        <v>976</v>
+        <v>837</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>2579</v>
+        <v>3257</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>897</v>
+        <v>1281</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>385</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>137</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7186</v>
+        <v>5554</v>
       </c>
       <c r="C2" t="n">
-        <v>2559</v>
+        <v>7371</v>
       </c>
       <c r="D2" t="n">
-        <v>22349</v>
+        <v>7558</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3205</v>
+        <v>3451</v>
       </c>
       <c r="C2" t="n">
-        <v>8159</v>
+        <v>3840</v>
       </c>
       <c r="D2" t="n">
-        <v>7397</v>
+        <v>9829</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3856</v>
+        <v>3342</v>
       </c>
       <c r="C3" t="n">
-        <v>6855</v>
+        <v>3359</v>
       </c>
       <c r="D3" t="n">
-        <v>14086</v>
+        <v>12470</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4181</v>
+        <v>3629</v>
       </c>
       <c r="C4" t="n">
-        <v>9519</v>
+        <v>4804</v>
       </c>
       <c r="D4" t="n">
-        <v>12672</v>
+        <v>10397</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1764</v>
+        <v>1673</v>
       </c>
       <c r="C5" t="n">
-        <v>11572</v>
+        <v>8095</v>
       </c>
       <c r="D5" t="n">
-        <v>6483</v>
+        <v>5225</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="C6" t="n">
-        <v>6649</v>
+        <v>6782</v>
       </c>
       <c r="D6" t="n">
-        <v>2180</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>2527</v>
+        <v>3191</v>
       </c>
       <c r="D7" t="n">
-        <v>573</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>879</v>
+        <v>1255</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>377</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
         <v>134</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7603</v>
+        <v>7579</v>
       </c>
       <c r="C2" t="n">
-        <v>4297</v>
+        <v>4558</v>
       </c>
       <c r="D2" t="n">
-        <v>27171</v>
+        <v>11173</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3052</v>
+        <v>2360</v>
       </c>
       <c r="C3" t="n">
-        <v>1289</v>
+        <v>3714</v>
       </c>
       <c r="D3" t="n">
-        <v>4393</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5259</v>
+        <v>5879</v>
       </c>
       <c r="C2" t="n">
-        <v>7430</v>
+        <v>5361</v>
       </c>
       <c r="D2" t="n">
-        <v>24002</v>
+        <v>10355</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4376</v>
+        <v>4077</v>
       </c>
       <c r="C3" t="n">
-        <v>2579</v>
+        <v>3651</v>
       </c>
       <c r="D3" t="n">
-        <v>7896</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1360</v>
+        <v>1059</v>
       </c>
       <c r="C4" t="n">
-        <v>800</v>
+        <v>2218</v>
       </c>
       <c r="D4" t="n">
-        <v>2066</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5517</v>
+        <v>5710</v>
       </c>
       <c r="C2" t="n">
-        <v>7372</v>
+        <v>9594</v>
       </c>
       <c r="D2" t="n">
-        <v>25535</v>
+        <v>17205</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3962</v>
+        <v>4076</v>
       </c>
       <c r="C3" t="n">
-        <v>4522</v>
+        <v>3967</v>
       </c>
       <c r="D3" t="n">
-        <v>9904</v>
+        <v>4209</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2441</v>
+        <v>2171</v>
       </c>
       <c r="C4" t="n">
-        <v>1790</v>
+        <v>2983</v>
       </c>
       <c r="D4" t="n">
-        <v>3122</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>606</v>
+        <v>495</v>
       </c>
       <c r="C5" t="n">
-        <v>534</v>
+        <v>1306</v>
       </c>
       <c r="D5" t="n">
-        <v>1308</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7608</v>
+        <v>5153</v>
       </c>
       <c r="C2" t="n">
-        <v>6830</v>
+        <v>7423</v>
       </c>
       <c r="D2" t="n">
-        <v>21800</v>
+        <v>13769</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3863</v>
+        <v>3987</v>
       </c>
       <c r="C3" t="n">
-        <v>5212</v>
+        <v>5973</v>
       </c>
       <c r="D3" t="n">
-        <v>11582</v>
+        <v>5888</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2730</v>
+        <v>2631</v>
       </c>
       <c r="C4" t="n">
-        <v>3221</v>
+        <v>3421</v>
       </c>
       <c r="D4" t="n">
-        <v>4264</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1249</v>
+        <v>1106</v>
       </c>
       <c r="C5" t="n">
-        <v>1168</v>
+        <v>2164</v>
       </c>
       <c r="D5" t="n">
-        <v>1569</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>325</v>
+        <v>278</v>
       </c>
       <c r="C6" t="n">
-        <v>418</v>
+        <v>809</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>7195</v>
       </c>
       <c r="C2" t="n">
-        <v>5776</v>
+        <v>9669</v>
       </c>
       <c r="D2" t="n">
-        <v>23340</v>
+        <v>27489</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4117</v>
+        <v>3331</v>
       </c>
       <c r="C3" t="n">
-        <v>4947</v>
+        <v>5507</v>
       </c>
       <c r="D3" t="n">
-        <v>11591</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2033</v>
+        <v>2067</v>
       </c>
       <c r="C4" t="n">
-        <v>3537</v>
+        <v>3980</v>
       </c>
       <c r="D4" t="n">
-        <v>4770</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1045</v>
+        <v>970</v>
       </c>
       <c r="C5" t="n">
-        <v>1626</v>
+        <v>2066</v>
       </c>
       <c r="D5" t="n">
-        <v>1597</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>368</v>
+        <v>329</v>
       </c>
       <c r="C6" t="n">
-        <v>536</v>
+        <v>1000</v>
       </c>
       <c r="D6" t="n">
-        <v>812</v>
+        <v>758</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>244</v>
+        <v>370</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6510</v>
+        <v>5531</v>
       </c>
       <c r="C2" t="n">
-        <v>5360</v>
+        <v>5455</v>
       </c>
       <c r="D2" t="n">
-        <v>27959</v>
+        <v>23897</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5227</v>
+        <v>4384</v>
       </c>
       <c r="C3" t="n">
-        <v>4714</v>
+        <v>6853</v>
       </c>
       <c r="D3" t="n">
-        <v>12711</v>
+        <v>9537</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2707</v>
+        <v>2349</v>
       </c>
       <c r="C4" t="n">
-        <v>4282</v>
+        <v>4835</v>
       </c>
       <c r="D4" t="n">
-        <v>5954</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="C5" t="n">
-        <v>2729</v>
+        <v>3162</v>
       </c>
       <c r="D5" t="n">
-        <v>2188</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>659</v>
+        <v>606</v>
       </c>
       <c r="C6" t="n">
-        <v>1157</v>
+        <v>1601</v>
       </c>
       <c r="D6" t="n">
-        <v>943</v>
+        <v>814</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>727</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>233</v>
+        <v>303</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6577</v>
+        <v>5404</v>
       </c>
       <c r="C2" t="n">
-        <v>6003</v>
+        <v>4981</v>
       </c>
       <c r="D2" t="n">
-        <v>25543</v>
+        <v>27026</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4823</v>
+        <v>4079</v>
       </c>
       <c r="C3" t="n">
-        <v>4385</v>
+        <v>5315</v>
       </c>
       <c r="D3" t="n">
-        <v>14235</v>
+        <v>11147</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3381</v>
+        <v>2908</v>
       </c>
       <c r="C4" t="n">
-        <v>4437</v>
+        <v>5831</v>
       </c>
       <c r="D4" t="n">
-        <v>7070</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1788</v>
+        <v>1640</v>
       </c>
       <c r="C5" t="n">
-        <v>3495</v>
+        <v>4027</v>
       </c>
       <c r="D5" t="n">
-        <v>2787</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>915</v>
+        <v>887</v>
       </c>
       <c r="C6" t="n">
-        <v>1988</v>
+        <v>2421</v>
       </c>
       <c r="D6" t="n">
-        <v>1156</v>
+        <v>904</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>804</v>
+        <v>1189</v>
       </c>
       <c r="D7" t="n">
-        <v>621</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>322</v>
+        <v>515</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_25_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5686</v>
+        <v>6231</v>
       </c>
       <c r="C2" t="n">
-        <v>5228</v>
+        <v>9463</v>
       </c>
       <c r="D2" t="n">
-        <v>25667</v>
+        <v>25512</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3865</v>
+        <v>3997</v>
       </c>
       <c r="C3" t="n">
-        <v>4487</v>
+        <v>8550</v>
       </c>
       <c r="D3" t="n">
-        <v>12775</v>
+        <v>10259</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2986</v>
+        <v>3307</v>
       </c>
       <c r="C4" t="n">
-        <v>5437</v>
+        <v>6507</v>
       </c>
       <c r="D4" t="n">
-        <v>5392</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1953</v>
+        <v>2012</v>
       </c>
       <c r="C5" t="n">
-        <v>4822</v>
+        <v>4759</v>
       </c>
       <c r="D5" t="n">
-        <v>2071</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1135</v>
+        <v>1167</v>
       </c>
       <c r="C6" t="n">
-        <v>3196</v>
+        <v>3203</v>
       </c>
       <c r="D6" t="n">
-        <v>1008</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>531</v>
+        <v>585</v>
       </c>
       <c r="C7" t="n">
-        <v>1792</v>
+        <v>1846</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="C8" t="n">
-        <v>826</v>
+        <v>870</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -951,7 +951,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6773</v>
+        <v>9824</v>
       </c>
       <c r="C2" t="n">
-        <v>7756</v>
+        <v>6843</v>
       </c>
       <c r="D2" t="n">
-        <v>20286</v>
+        <v>22981</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3820</v>
+        <v>4068</v>
       </c>
       <c r="C3" t="n">
-        <v>4244</v>
+        <v>7889</v>
       </c>
       <c r="D3" t="n">
-        <v>13669</v>
+        <v>11644</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2884</v>
+        <v>3120</v>
       </c>
       <c r="C4" t="n">
-        <v>4815</v>
+        <v>7289</v>
       </c>
       <c r="D4" t="n">
-        <v>6381</v>
+        <v>4947</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2143</v>
+        <v>2261</v>
       </c>
       <c r="C5" t="n">
-        <v>5010</v>
+        <v>5482</v>
       </c>
       <c r="D5" t="n">
-        <v>2550</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1354</v>
+        <v>1393</v>
       </c>
       <c r="C6" t="n">
-        <v>3867</v>
+        <v>3842</v>
       </c>
       <c r="D6" t="n">
-        <v>1147</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>707</v>
+        <v>750</v>
       </c>
       <c r="C7" t="n">
-        <v>2424</v>
+        <v>2456</v>
       </c>
       <c r="D7" t="n">
-        <v>690</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="C8" t="n">
-        <v>1234</v>
+        <v>1281</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1262,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7676</v>
+        <v>9929</v>
       </c>
       <c r="C2" t="n">
-        <v>6101</v>
+        <v>15154</v>
       </c>
       <c r="D2" t="n">
-        <v>24118</v>
+        <v>26616</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4098</v>
+        <v>5135</v>
       </c>
       <c r="C3" t="n">
-        <v>5054</v>
+        <v>6607</v>
       </c>
       <c r="D3" t="n">
-        <v>13619</v>
+        <v>12443</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2817</v>
+        <v>2991</v>
       </c>
       <c r="C4" t="n">
-        <v>4416</v>
+        <v>7402</v>
       </c>
       <c r="D4" t="n">
-        <v>7306</v>
+        <v>5713</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2176</v>
+        <v>2320</v>
       </c>
       <c r="C5" t="n">
-        <v>4821</v>
+        <v>6078</v>
       </c>
       <c r="D5" t="n">
-        <v>2999</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1526</v>
+        <v>1601</v>
       </c>
       <c r="C6" t="n">
-        <v>4266</v>
+        <v>4484</v>
       </c>
       <c r="D6" t="n">
-        <v>1333</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>869</v>
+        <v>901</v>
       </c>
       <c r="C7" t="n">
-        <v>2993</v>
+        <v>2987</v>
       </c>
       <c r="D7" t="n">
-        <v>738</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>408</v>
+        <v>439</v>
       </c>
       <c r="C8" t="n">
-        <v>1711</v>
+        <v>1728</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C9" t="n">
-        <v>814</v>
+        <v>848</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
         <v>127</v>
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1590,7 +1590,7 @@
         <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7024</v>
+        <v>9091</v>
       </c>
       <c r="C2" t="n">
-        <v>4099</v>
+        <v>10304</v>
       </c>
       <c r="D2" t="n">
-        <v>19817</v>
+        <v>21890</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5018</v>
+        <v>5785</v>
       </c>
       <c r="C3" t="n">
-        <v>7413</v>
+        <v>11216</v>
       </c>
       <c r="D3" t="n">
-        <v>14725</v>
+        <v>13103</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2010</v>
+        <v>2143</v>
       </c>
       <c r="C4" t="n">
-        <v>7086</v>
+        <v>9885</v>
       </c>
       <c r="D4" t="n">
-        <v>6883</v>
+        <v>5363</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1410</v>
+        <v>1479</v>
       </c>
       <c r="C5" t="n">
-        <v>4180</v>
+        <v>4394</v>
       </c>
       <c r="D5" t="n">
-        <v>2141</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>802</v>
+        <v>832</v>
       </c>
       <c r="C6" t="n">
-        <v>2933</v>
+        <v>2927</v>
       </c>
       <c r="D6" t="n">
-        <v>723</v>
+        <v>679</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="C7" t="n">
-        <v>1676</v>
+        <v>1693</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="C8" t="n">
-        <v>797</v>
+        <v>831</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>124</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1887,7 +1887,7 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4351</v>
+        <v>5448</v>
       </c>
       <c r="C2" t="n">
-        <v>3263</v>
+        <v>4704</v>
       </c>
       <c r="D2" t="n">
-        <v>13941</v>
+        <v>15098</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5082</v>
+        <v>6162</v>
       </c>
       <c r="C3" t="n">
-        <v>5334</v>
+        <v>9885</v>
       </c>
       <c r="D3" t="n">
-        <v>14569</v>
+        <v>13543</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2763</v>
+        <v>3045</v>
       </c>
       <c r="C4" t="n">
-        <v>7296</v>
+        <v>10577</v>
       </c>
       <c r="D4" t="n">
-        <v>8010</v>
+        <v>6491</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1565</v>
+        <v>1645</v>
       </c>
       <c r="C5" t="n">
-        <v>5521</v>
+        <v>6780</v>
       </c>
       <c r="D5" t="n">
-        <v>2708</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>961</v>
+        <v>987</v>
       </c>
       <c r="C6" t="n">
-        <v>3554</v>
+        <v>3583</v>
       </c>
       <c r="D6" t="n">
-        <v>871</v>
+        <v>795</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="C7" t="n">
-        <v>2151</v>
+        <v>2180</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>1071</v>
+        <v>1097</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D9" t="n">
         <v>260</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2184,7 +2184,7 @@
         <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5086</v>
+        <v>5293</v>
       </c>
       <c r="C2" t="n">
-        <v>4490</v>
+        <v>11026</v>
       </c>
       <c r="D2" t="n">
-        <v>17927</v>
+        <v>20754</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3999</v>
+        <v>4928</v>
       </c>
       <c r="C3" t="n">
-        <v>3841</v>
+        <v>6606</v>
       </c>
       <c r="D3" t="n">
-        <v>13476</v>
+        <v>12844</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3274</v>
+        <v>3735</v>
       </c>
       <c r="C4" t="n">
-        <v>6164</v>
+        <v>10018</v>
       </c>
       <c r="D4" t="n">
-        <v>8899</v>
+        <v>7444</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1852</v>
+        <v>1984</v>
       </c>
       <c r="C5" t="n">
-        <v>6258</v>
+        <v>8490</v>
       </c>
       <c r="D5" t="n">
-        <v>3490</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1129</v>
+        <v>1167</v>
       </c>
       <c r="C6" t="n">
-        <v>4459</v>
+        <v>4960</v>
       </c>
       <c r="D6" t="n">
-        <v>1141</v>
+        <v>987</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="C7" t="n">
-        <v>2789</v>
+        <v>2805</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C8" t="n">
-        <v>1525</v>
+        <v>1542</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
         <v>677</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2495,7 +2495,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2988</v>
+        <v>3199</v>
       </c>
       <c r="C2" t="n">
-        <v>2091</v>
+        <v>5256</v>
       </c>
       <c r="D2" t="n">
-        <v>12364</v>
+        <v>14464</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4116</v>
+        <v>4838</v>
       </c>
       <c r="C3" t="n">
-        <v>3904</v>
+        <v>7865</v>
       </c>
       <c r="D3" t="n">
-        <v>13651</v>
+        <v>13378</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3625</v>
+        <v>4113</v>
       </c>
       <c r="C4" t="n">
-        <v>5883</v>
+        <v>9690</v>
       </c>
       <c r="D4" t="n">
-        <v>9495</v>
+        <v>8068</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1959</v>
+        <v>2062</v>
       </c>
       <c r="C5" t="n">
-        <v>7122</v>
+        <v>10054</v>
       </c>
       <c r="D5" t="n">
-        <v>3803</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>949</v>
+        <v>965</v>
       </c>
       <c r="C6" t="n">
-        <v>5462</v>
+        <v>5883</v>
       </c>
       <c r="D6" t="n">
-        <v>1138</v>
+        <v>992</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>2902</v>
+        <v>2884</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1141</v>
+        <v>1131</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2792,7 +2792,7 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3960</v>
+        <v>3780</v>
       </c>
       <c r="C2" t="n">
-        <v>2475</v>
+        <v>7760</v>
       </c>
       <c r="D2" t="n">
-        <v>15798</v>
+        <v>18327</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3072</v>
+        <v>3538</v>
       </c>
       <c r="C3" t="n">
-        <v>2706</v>
+        <v>5986</v>
       </c>
       <c r="D3" t="n">
-        <v>12558</v>
+        <v>12755</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3383</v>
+        <v>3885</v>
       </c>
       <c r="C4" t="n">
-        <v>4848</v>
+        <v>8647</v>
       </c>
       <c r="D4" t="n">
-        <v>9884</v>
+        <v>8638</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2355</v>
+        <v>2541</v>
       </c>
       <c r="C5" t="n">
-        <v>6471</v>
+        <v>9780</v>
       </c>
       <c r="D5" t="n">
-        <v>4561</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1228</v>
+        <v>1250</v>
       </c>
       <c r="C6" t="n">
-        <v>6181</v>
+        <v>7609</v>
       </c>
       <c r="D6" t="n">
-        <v>1517</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C7" t="n">
-        <v>4011</v>
+        <v>4114</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1818</v>
+        <v>1771</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>587</v>
+        <v>564</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>59</v>
+      </c>
+      <c r="D13" t="n">
         <v>61</v>
-      </c>
-      <c r="D13" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2800</v>
+        <v>2843</v>
       </c>
       <c r="C2" t="n">
-        <v>2246</v>
+        <v>4145</v>
       </c>
       <c r="D2" t="n">
-        <v>12549</v>
+        <v>13448</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2951</v>
+        <v>3168</v>
       </c>
       <c r="C3" t="n">
-        <v>2365</v>
+        <v>6059</v>
       </c>
       <c r="D3" t="n">
-        <v>12263</v>
+        <v>12705</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3028</v>
+        <v>3489</v>
       </c>
       <c r="C4" t="n">
-        <v>3982</v>
+        <v>7668</v>
       </c>
       <c r="D4" t="n">
-        <v>10037</v>
+        <v>8972</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2563</v>
+        <v>2761</v>
       </c>
       <c r="C5" t="n">
-        <v>5977</v>
+        <v>9466</v>
       </c>
       <c r="D5" t="n">
-        <v>5123</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1440</v>
+        <v>1466</v>
       </c>
       <c r="C6" t="n">
-        <v>6532</v>
+        <v>8577</v>
       </c>
       <c r="D6" t="n">
-        <v>1791</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>4837</v>
+        <v>5216</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>2360</v>
+        <v>2304</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>709</v>
+        <v>638</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4878</v>
+        <v>4000</v>
       </c>
       <c r="C2" t="n">
-        <v>6858</v>
+        <v>16378</v>
       </c>
       <c r="D2" t="n">
-        <v>13355</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2435</v>
+        <v>2577</v>
       </c>
       <c r="C3" t="n">
-        <v>2052</v>
+        <v>4741</v>
       </c>
       <c r="D3" t="n">
-        <v>11495</v>
+        <v>12103</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2607</v>
+        <v>2939</v>
       </c>
       <c r="C4" t="n">
-        <v>3185</v>
+        <v>6844</v>
       </c>
       <c r="D4" t="n">
-        <v>10073</v>
+        <v>9114</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2489</v>
+        <v>2737</v>
       </c>
       <c r="C5" t="n">
-        <v>5009</v>
+        <v>8561</v>
       </c>
       <c r="D5" t="n">
-        <v>5674</v>
+        <v>4635</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1712</v>
+        <v>1754</v>
       </c>
       <c r="C6" t="n">
-        <v>6250</v>
+        <v>8839</v>
       </c>
       <c r="D6" t="n">
-        <v>2215</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>635</v>
+        <v>594</v>
       </c>
       <c r="C7" t="n">
-        <v>5546</v>
+        <v>6483</v>
       </c>
       <c r="D7" t="n">
-        <v>837</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C8" t="n">
-        <v>3257</v>
+        <v>3273</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1281</v>
+        <v>1166</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>385</v>
+        <v>343</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5554</v>
+        <v>7881</v>
       </c>
       <c r="C2" t="n">
-        <v>7371</v>
+        <v>6286</v>
       </c>
       <c r="D2" t="n">
-        <v>7558</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3451</v>
+        <v>2927</v>
       </c>
       <c r="C2" t="n">
-        <v>3840</v>
+        <v>9565</v>
       </c>
       <c r="D2" t="n">
-        <v>9829</v>
+        <v>7945</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3342</v>
+        <v>3460</v>
       </c>
       <c r="C3" t="n">
-        <v>3359</v>
+        <v>7745</v>
       </c>
       <c r="D3" t="n">
-        <v>12470</v>
+        <v>12916</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3629</v>
+        <v>4031</v>
       </c>
       <c r="C4" t="n">
-        <v>4804</v>
+        <v>9708</v>
       </c>
       <c r="D4" t="n">
-        <v>10397</v>
+        <v>9161</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1673</v>
+        <v>1645</v>
       </c>
       <c r="C5" t="n">
-        <v>8095</v>
+        <v>12527</v>
       </c>
       <c r="D5" t="n">
-        <v>5225</v>
+        <v>4211</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>586</v>
+        <v>548</v>
       </c>
       <c r="C6" t="n">
-        <v>6782</v>
+        <v>7912</v>
       </c>
       <c r="D6" t="n">
-        <v>1790</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>3191</v>
+        <v>3207</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1255</v>
+        <v>1142</v>
       </c>
       <c r="D8" t="n">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>377</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7579</v>
+        <v>7717</v>
       </c>
       <c r="C2" t="n">
-        <v>4558</v>
+        <v>6240</v>
       </c>
       <c r="D2" t="n">
-        <v>11173</v>
+        <v>9696</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2360</v>
+        <v>3347</v>
       </c>
       <c r="C3" t="n">
-        <v>3714</v>
+        <v>3218</v>
       </c>
       <c r="D3" t="n">
-        <v>1909</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5879</v>
+        <v>5155</v>
       </c>
       <c r="C2" t="n">
-        <v>5361</v>
+        <v>7232</v>
       </c>
       <c r="D2" t="n">
-        <v>10355</v>
+        <v>8908</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4077</v>
+        <v>4545</v>
       </c>
       <c r="C3" t="n">
-        <v>3651</v>
+        <v>4268</v>
       </c>
       <c r="D3" t="n">
-        <v>3324</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1059</v>
+        <v>1487</v>
       </c>
       <c r="C4" t="n">
-        <v>2218</v>
+        <v>1959</v>
       </c>
       <c r="D4" t="n">
-        <v>1566</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="5">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5710</v>
+        <v>4856</v>
       </c>
       <c r="C2" t="n">
-        <v>9594</v>
+        <v>5300</v>
       </c>
       <c r="D2" t="n">
-        <v>17205</v>
+        <v>11185</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4076</v>
+        <v>3995</v>
       </c>
       <c r="C3" t="n">
-        <v>3967</v>
+        <v>5093</v>
       </c>
       <c r="D3" t="n">
-        <v>4209</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2171</v>
+        <v>2556</v>
       </c>
       <c r="C4" t="n">
-        <v>2983</v>
+        <v>3226</v>
       </c>
       <c r="D4" t="n">
-        <v>1855</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>495</v>
+        <v>670</v>
       </c>
       <c r="C5" t="n">
-        <v>1306</v>
+        <v>1164</v>
       </c>
       <c r="D5" t="n">
-        <v>1207</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="6">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5153</v>
+        <v>5458</v>
       </c>
       <c r="C2" t="n">
-        <v>7423</v>
+        <v>9713</v>
       </c>
       <c r="D2" t="n">
-        <v>13769</v>
+        <v>15252</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3987</v>
+        <v>3629</v>
       </c>
       <c r="C3" t="n">
-        <v>5973</v>
+        <v>4519</v>
       </c>
       <c r="D3" t="n">
-        <v>5888</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2631</v>
+        <v>2775</v>
       </c>
       <c r="C4" t="n">
-        <v>3421</v>
+        <v>4180</v>
       </c>
       <c r="D4" t="n">
-        <v>2210</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1106</v>
+        <v>1348</v>
       </c>
       <c r="C5" t="n">
-        <v>2164</v>
+        <v>2228</v>
       </c>
       <c r="D5" t="n">
-        <v>1288</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>278</v>
+        <v>349</v>
       </c>
       <c r="C6" t="n">
-        <v>809</v>
+        <v>734</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>943</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
         <v>659</v>
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7195</v>
+        <v>8083</v>
       </c>
       <c r="C2" t="n">
-        <v>9669</v>
+        <v>8606</v>
       </c>
       <c r="D2" t="n">
-        <v>27489</v>
+        <v>16236</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3331</v>
+        <v>3302</v>
       </c>
       <c r="C3" t="n">
-        <v>5507</v>
+        <v>5914</v>
       </c>
       <c r="D3" t="n">
-        <v>6276</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2067</v>
+        <v>2002</v>
       </c>
       <c r="C4" t="n">
-        <v>3980</v>
+        <v>3584</v>
       </c>
       <c r="D4" t="n">
-        <v>2435</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>970</v>
+        <v>1080</v>
       </c>
       <c r="C5" t="n">
-        <v>2066</v>
+        <v>2383</v>
       </c>
       <c r="D5" t="n">
-        <v>1148</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>329</v>
+        <v>404</v>
       </c>
       <c r="C6" t="n">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="D6" t="n">
-        <v>758</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5531</v>
+        <v>6653</v>
       </c>
       <c r="C2" t="n">
-        <v>5455</v>
+        <v>10355</v>
       </c>
       <c r="D2" t="n">
-        <v>23897</v>
+        <v>19383</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4384</v>
+        <v>4785</v>
       </c>
       <c r="C3" t="n">
-        <v>6853</v>
+        <v>6450</v>
       </c>
       <c r="D3" t="n">
-        <v>9537</v>
+        <v>6832</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2349</v>
+        <v>2337</v>
       </c>
       <c r="C4" t="n">
-        <v>4835</v>
+        <v>4941</v>
       </c>
       <c r="D4" t="n">
-        <v>3172</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1363</v>
+        <v>1385</v>
       </c>
       <c r="C5" t="n">
-        <v>3162</v>
+        <v>3025</v>
       </c>
       <c r="D5" t="n">
-        <v>1372</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>606</v>
+        <v>689</v>
       </c>
       <c r="C6" t="n">
-        <v>1601</v>
+        <v>1796</v>
       </c>
       <c r="D6" t="n">
-        <v>814</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="C7" t="n">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6199,7 +6199,7 @@
         <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6241,7 +6241,7 @@
         <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5404</v>
+        <v>4987</v>
       </c>
       <c r="C2" t="n">
-        <v>4981</v>
+        <v>12122</v>
       </c>
       <c r="D2" t="n">
-        <v>27026</v>
+        <v>24788</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4079</v>
+        <v>4699</v>
       </c>
       <c r="C3" t="n">
-        <v>5315</v>
+        <v>7447</v>
       </c>
       <c r="D3" t="n">
-        <v>11147</v>
+        <v>8348</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2908</v>
+        <v>3073</v>
       </c>
       <c r="C4" t="n">
-        <v>5831</v>
+        <v>5707</v>
       </c>
       <c r="D4" t="n">
-        <v>4267</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1640</v>
+        <v>1634</v>
       </c>
       <c r="C5" t="n">
-        <v>4027</v>
+        <v>4028</v>
       </c>
       <c r="D5" t="n">
-        <v>1675</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>887</v>
+        <v>951</v>
       </c>
       <c r="C6" t="n">
-        <v>2421</v>
+        <v>2435</v>
       </c>
       <c r="D6" t="n">
-        <v>904</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352</v>
+        <v>407</v>
       </c>
       <c r="C7" t="n">
-        <v>1189</v>
+        <v>1282</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C8" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>

--- a/output/yearly_population_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_25_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6231</v>
+        <v>1205</v>
       </c>
       <c r="C2" t="n">
-        <v>9463</v>
+        <v>4631</v>
       </c>
       <c r="D2" t="n">
-        <v>25512</v>
+        <v>19169</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3997</v>
+        <v>1913</v>
       </c>
       <c r="C3" t="n">
-        <v>8550</v>
+        <v>10309</v>
       </c>
       <c r="D3" t="n">
-        <v>10259</v>
+        <v>13510</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3307</v>
+        <v>1280</v>
       </c>
       <c r="C4" t="n">
-        <v>6507</v>
+        <v>12292</v>
       </c>
       <c r="D4" t="n">
-        <v>4108</v>
+        <v>5163</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2012</v>
+        <v>656</v>
       </c>
       <c r="C5" t="n">
-        <v>4759</v>
+        <v>8810</v>
       </c>
       <c r="D5" t="n">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1167</v>
+        <v>274</v>
       </c>
       <c r="C6" t="n">
-        <v>3203</v>
+        <v>3849</v>
       </c>
       <c r="D6" t="n">
-        <v>931</v>
+        <v>706</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>585</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1846</v>
+        <v>1171</v>
       </c>
       <c r="D7" t="n">
-        <v>623</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>226</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>870</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>371</v>
+        <v>261</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>51</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9824</v>
+        <v>1248</v>
       </c>
       <c r="C2" t="n">
-        <v>6843</v>
+        <v>6577</v>
       </c>
       <c r="D2" t="n">
-        <v>22981</v>
+        <v>15114</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4068</v>
+        <v>1359</v>
       </c>
       <c r="C3" t="n">
-        <v>7889</v>
+        <v>6713</v>
       </c>
       <c r="D3" t="n">
-        <v>11644</v>
+        <v>13525</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3120</v>
+        <v>1349</v>
       </c>
       <c r="C4" t="n">
-        <v>7289</v>
+        <v>11046</v>
       </c>
       <c r="D4" t="n">
-        <v>4947</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2261</v>
+        <v>813</v>
       </c>
       <c r="C5" t="n">
-        <v>5482</v>
+        <v>10382</v>
       </c>
       <c r="D5" t="n">
-        <v>2025</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1393</v>
+        <v>387</v>
       </c>
       <c r="C6" t="n">
-        <v>3842</v>
+        <v>6087</v>
       </c>
       <c r="D6" t="n">
-        <v>1033</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>750</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>2456</v>
+        <v>2325</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>335</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1281</v>
+        <v>712</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>581</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9929</v>
+        <v>701</v>
       </c>
       <c r="C2" t="n">
-        <v>15154</v>
+        <v>3058</v>
       </c>
       <c r="D2" t="n">
-        <v>26616</v>
+        <v>10448</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5135</v>
+        <v>1295</v>
       </c>
       <c r="C3" t="n">
-        <v>6607</v>
+        <v>6451</v>
       </c>
       <c r="D3" t="n">
-        <v>12443</v>
+        <v>13378</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2991</v>
+        <v>1461</v>
       </c>
       <c r="C4" t="n">
-        <v>7402</v>
+        <v>10420</v>
       </c>
       <c r="D4" t="n">
-        <v>5713</v>
+        <v>7142</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2320</v>
+        <v>801</v>
       </c>
       <c r="C5" t="n">
-        <v>6078</v>
+        <v>12105</v>
       </c>
       <c r="D5" t="n">
-        <v>2364</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1601</v>
+        <v>293</v>
       </c>
       <c r="C6" t="n">
-        <v>4484</v>
+        <v>6994</v>
       </c>
       <c r="D6" t="n">
-        <v>1162</v>
+        <v>862</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>901</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>2987</v>
+        <v>2030</v>
       </c>
       <c r="D7" t="n">
-        <v>693</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>439</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1728</v>
+        <v>517</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>176</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>848</v>
+        <v>223</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>383</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9091</v>
+        <v>844</v>
       </c>
       <c r="C2" t="n">
-        <v>10304</v>
+        <v>7027</v>
       </c>
       <c r="D2" t="n">
-        <v>21890</v>
+        <v>10131</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5785</v>
+        <v>902</v>
       </c>
       <c r="C3" t="n">
-        <v>11216</v>
+        <v>4381</v>
       </c>
       <c r="D3" t="n">
-        <v>13103</v>
+        <v>12080</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2143</v>
+        <v>1226</v>
       </c>
       <c r="C4" t="n">
-        <v>9885</v>
+        <v>8336</v>
       </c>
       <c r="D4" t="n">
-        <v>5363</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1479</v>
+        <v>951</v>
       </c>
       <c r="C5" t="n">
-        <v>4394</v>
+        <v>11209</v>
       </c>
       <c r="D5" t="n">
-        <v>1774</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>832</v>
+        <v>434</v>
       </c>
       <c r="C6" t="n">
-        <v>2927</v>
+        <v>9225</v>
       </c>
       <c r="D6" t="n">
-        <v>679</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>1693</v>
+        <v>3994</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>831</v>
+        <v>1080</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>375</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
+        <v>76</v>
+      </c>
+      <c r="D13" t="n">
         <v>89</v>
-      </c>
-      <c r="D13" t="n">
-        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5448</v>
+        <v>572</v>
       </c>
       <c r="C2" t="n">
-        <v>4704</v>
+        <v>5061</v>
       </c>
       <c r="D2" t="n">
-        <v>15098</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6162</v>
+        <v>774</v>
       </c>
       <c r="C3" t="n">
-        <v>9885</v>
+        <v>4969</v>
       </c>
       <c r="D3" t="n">
-        <v>13543</v>
+        <v>11188</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3045</v>
+        <v>1045</v>
       </c>
       <c r="C4" t="n">
-        <v>10577</v>
+        <v>6808</v>
       </c>
       <c r="D4" t="n">
-        <v>6491</v>
+        <v>8468</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1645</v>
+        <v>994</v>
       </c>
       <c r="C5" t="n">
-        <v>6780</v>
+        <v>10278</v>
       </c>
       <c r="D5" t="n">
-        <v>2202</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>987</v>
+        <v>524</v>
       </c>
       <c r="C6" t="n">
-        <v>3583</v>
+        <v>10314</v>
       </c>
       <c r="D6" t="n">
-        <v>795</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>383</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>2180</v>
+        <v>5496</v>
       </c>
       <c r="D7" t="n">
-        <v>504</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1097</v>
+        <v>1618</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>423</v>
+        <v>385</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5293</v>
+        <v>544</v>
       </c>
       <c r="C2" t="n">
-        <v>11026</v>
+        <v>8611</v>
       </c>
       <c r="D2" t="n">
-        <v>20754</v>
+        <v>10376</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4928</v>
+        <v>591</v>
       </c>
       <c r="C3" t="n">
-        <v>6606</v>
+        <v>4493</v>
       </c>
       <c r="D3" t="n">
-        <v>12844</v>
+        <v>10016</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3735</v>
+        <v>833</v>
       </c>
       <c r="C4" t="n">
-        <v>10018</v>
+        <v>5889</v>
       </c>
       <c r="D4" t="n">
-        <v>7444</v>
+        <v>8602</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1984</v>
+        <v>927</v>
       </c>
       <c r="C5" t="n">
-        <v>8490</v>
+        <v>8665</v>
       </c>
       <c r="D5" t="n">
-        <v>2793</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1167</v>
+        <v>633</v>
       </c>
       <c r="C6" t="n">
-        <v>4960</v>
+        <v>10213</v>
       </c>
       <c r="D6" t="n">
-        <v>987</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>543</v>
+        <v>216</v>
       </c>
       <c r="C7" t="n">
-        <v>2805</v>
+        <v>7341</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>196</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1542</v>
+        <v>2947</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>677</v>
+        <v>787</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2495,7 +2495,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
+        <v>64</v>
+      </c>
+      <c r="D14" t="n">
         <v>53</v>
-      </c>
-      <c r="D14" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3199</v>
+        <v>387</v>
       </c>
       <c r="C2" t="n">
-        <v>5256</v>
+        <v>4959</v>
       </c>
       <c r="D2" t="n">
-        <v>14464</v>
+        <v>7636</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4838</v>
+        <v>821</v>
       </c>
       <c r="C3" t="n">
-        <v>7865</v>
+        <v>5810</v>
       </c>
       <c r="D3" t="n">
-        <v>13378</v>
+        <v>10857</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4113</v>
+        <v>1279</v>
       </c>
       <c r="C4" t="n">
-        <v>9690</v>
+        <v>8829</v>
       </c>
       <c r="D4" t="n">
-        <v>8068</v>
+        <v>8652</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2062</v>
+        <v>602</v>
       </c>
       <c r="C5" t="n">
-        <v>10054</v>
+        <v>13680</v>
       </c>
       <c r="D5" t="n">
-        <v>2975</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>965</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>5883</v>
+        <v>9095</v>
       </c>
       <c r="D6" t="n">
-        <v>992</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>56</v>
       </c>
       <c r="C7" t="n">
-        <v>2884</v>
+        <v>2888</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1131</v>
+        <v>771</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2792,7 +2792,7 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D13" t="n">
         <v>51</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3780</v>
+        <v>214</v>
       </c>
       <c r="C2" t="n">
-        <v>7760</v>
+        <v>3176</v>
       </c>
       <c r="D2" t="n">
-        <v>18327</v>
+        <v>6142</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3538</v>
+        <v>554</v>
       </c>
       <c r="C3" t="n">
-        <v>5986</v>
+        <v>4822</v>
       </c>
       <c r="D3" t="n">
-        <v>12755</v>
+        <v>9698</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3885</v>
+        <v>896</v>
       </c>
       <c r="C4" t="n">
-        <v>8647</v>
+        <v>6948</v>
       </c>
       <c r="D4" t="n">
-        <v>8638</v>
+        <v>8358</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2541</v>
+        <v>598</v>
       </c>
       <c r="C5" t="n">
-        <v>9780</v>
+        <v>10258</v>
       </c>
       <c r="D5" t="n">
-        <v>3617</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1250</v>
+        <v>193</v>
       </c>
       <c r="C6" t="n">
-        <v>7609</v>
+        <v>8896</v>
       </c>
       <c r="D6" t="n">
-        <v>1245</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>363</v>
+        <v>43</v>
       </c>
       <c r="C7" t="n">
-        <v>4114</v>
+        <v>3769</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>1771</v>
+        <v>943</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>564</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>107</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2843</v>
+        <v>209</v>
       </c>
       <c r="C2" t="n">
-        <v>4145</v>
+        <v>13426</v>
       </c>
       <c r="D2" t="n">
-        <v>13448</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3168</v>
+        <v>341</v>
       </c>
       <c r="C3" t="n">
-        <v>6059</v>
+        <v>3501</v>
       </c>
       <c r="D3" t="n">
-        <v>12705</v>
+        <v>8518</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3489</v>
+        <v>650</v>
       </c>
       <c r="C4" t="n">
-        <v>7668</v>
+        <v>5701</v>
       </c>
       <c r="D4" t="n">
-        <v>8972</v>
+        <v>8335</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2761</v>
+        <v>657</v>
       </c>
       <c r="C5" t="n">
-        <v>9466</v>
+        <v>8490</v>
       </c>
       <c r="D5" t="n">
-        <v>4106</v>
+        <v>4446</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1466</v>
+        <v>329</v>
       </c>
       <c r="C6" t="n">
-        <v>8577</v>
+        <v>9445</v>
       </c>
       <c r="D6" t="n">
-        <v>1436</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>5216</v>
+        <v>6165</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>2304</v>
+        <v>2170</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>638</v>
+        <v>527</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4000</v>
+        <v>218</v>
       </c>
       <c r="C2" t="n">
-        <v>16378</v>
+        <v>10382</v>
       </c>
       <c r="D2" t="n">
-        <v>10680</v>
+        <v>12093</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2577</v>
+        <v>241</v>
       </c>
       <c r="C3" t="n">
-        <v>4741</v>
+        <v>7010</v>
       </c>
       <c r="D3" t="n">
-        <v>12103</v>
+        <v>8328</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2939</v>
+        <v>454</v>
       </c>
       <c r="C4" t="n">
-        <v>6844</v>
+        <v>4513</v>
       </c>
       <c r="D4" t="n">
-        <v>9114</v>
+        <v>8029</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2737</v>
+        <v>598</v>
       </c>
       <c r="C5" t="n">
-        <v>8561</v>
+        <v>7055</v>
       </c>
       <c r="D5" t="n">
-        <v>4635</v>
+        <v>4908</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1754</v>
+        <v>422</v>
       </c>
       <c r="C6" t="n">
-        <v>8839</v>
+        <v>8943</v>
       </c>
       <c r="D6" t="n">
-        <v>1750</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>594</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>6483</v>
+        <v>7484</v>
       </c>
       <c r="D7" t="n">
-        <v>742</v>
+        <v>784</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>3273</v>
+        <v>3813</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7881</v>
+        <v>5706</v>
       </c>
       <c r="C2" t="n">
-        <v>6286</v>
+        <v>27865</v>
       </c>
       <c r="D2" t="n">
-        <v>2572</v>
+        <v>8712</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2927</v>
+        <v>430</v>
       </c>
       <c r="C2" t="n">
-        <v>9565</v>
+        <v>14414</v>
       </c>
       <c r="D2" t="n">
-        <v>7945</v>
+        <v>11865</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3460</v>
+        <v>194</v>
       </c>
       <c r="C3" t="n">
-        <v>7745</v>
+        <v>7407</v>
       </c>
       <c r="D3" t="n">
-        <v>12916</v>
+        <v>8246</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4031</v>
+        <v>329</v>
       </c>
       <c r="C4" t="n">
-        <v>9708</v>
+        <v>5406</v>
       </c>
       <c r="D4" t="n">
-        <v>9161</v>
+        <v>7827</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1645</v>
+        <v>501</v>
       </c>
       <c r="C5" t="n">
-        <v>12527</v>
+        <v>5883</v>
       </c>
       <c r="D5" t="n">
-        <v>4211</v>
+        <v>5131</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>548</v>
+        <v>447</v>
       </c>
       <c r="C6" t="n">
-        <v>7912</v>
+        <v>8055</v>
       </c>
       <c r="D6" t="n">
-        <v>1472</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>110</v>
+        <v>229</v>
       </c>
       <c r="C7" t="n">
-        <v>3207</v>
+        <v>8038</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>933</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>1142</v>
+        <v>5105</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>2101</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>583</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
         <v>36</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7717</v>
+        <v>4829</v>
       </c>
       <c r="C2" t="n">
-        <v>6240</v>
+        <v>18427</v>
       </c>
       <c r="D2" t="n">
-        <v>9696</v>
+        <v>14743</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3347</v>
+        <v>1839</v>
       </c>
       <c r="C3" t="n">
-        <v>3218</v>
+        <v>11004</v>
       </c>
       <c r="D3" t="n">
-        <v>1092</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5155</v>
+        <v>2685</v>
       </c>
       <c r="C2" t="n">
-        <v>7232</v>
+        <v>11951</v>
       </c>
       <c r="D2" t="n">
-        <v>8908</v>
+        <v>19960</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4545</v>
+        <v>2783</v>
       </c>
       <c r="C3" t="n">
-        <v>4268</v>
+        <v>13237</v>
       </c>
       <c r="D3" t="n">
-        <v>2457</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1487</v>
+        <v>860</v>
       </c>
       <c r="C4" t="n">
-        <v>1959</v>
+        <v>6809</v>
       </c>
       <c r="D4" t="n">
-        <v>1401</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4856</v>
+        <v>1415</v>
       </c>
       <c r="C2" t="n">
-        <v>5300</v>
+        <v>5480</v>
       </c>
       <c r="D2" t="n">
-        <v>11185</v>
+        <v>21128</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3995</v>
+        <v>2259</v>
       </c>
       <c r="C3" t="n">
-        <v>5093</v>
+        <v>10819</v>
       </c>
       <c r="D3" t="n">
-        <v>3312</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2556</v>
+        <v>1566</v>
       </c>
       <c r="C4" t="n">
-        <v>3226</v>
+        <v>10369</v>
       </c>
       <c r="D4" t="n">
-        <v>1561</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>670</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>1164</v>
+        <v>3879</v>
       </c>
       <c r="D5" t="n">
-        <v>1177</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>797</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5458</v>
+        <v>3027</v>
       </c>
       <c r="C2" t="n">
-        <v>9713</v>
+        <v>9393</v>
       </c>
       <c r="D2" t="n">
-        <v>15252</v>
+        <v>22355</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3629</v>
+        <v>1552</v>
       </c>
       <c r="C3" t="n">
-        <v>4519</v>
+        <v>7024</v>
       </c>
       <c r="D3" t="n">
-        <v>4275</v>
+        <v>8052</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2775</v>
+        <v>1638</v>
       </c>
       <c r="C4" t="n">
-        <v>4180</v>
+        <v>10395</v>
       </c>
       <c r="D4" t="n">
-        <v>1817</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1348</v>
+        <v>807</v>
       </c>
       <c r="C5" t="n">
-        <v>2228</v>
+        <v>7162</v>
       </c>
       <c r="D5" t="n">
-        <v>1211</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>349</v>
+        <v>222</v>
       </c>
       <c r="C6" t="n">
-        <v>734</v>
+        <v>2064</v>
       </c>
       <c r="D6" t="n">
-        <v>943</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>298</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8083</v>
+        <v>2484</v>
       </c>
       <c r="C2" t="n">
-        <v>8606</v>
+        <v>9213</v>
       </c>
       <c r="D2" t="n">
-        <v>16236</v>
+        <v>28792</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3302</v>
+        <v>1795</v>
       </c>
       <c r="C3" t="n">
-        <v>5914</v>
+        <v>7144</v>
       </c>
       <c r="D3" t="n">
-        <v>5308</v>
+        <v>9557</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2002</v>
+        <v>1378</v>
       </c>
       <c r="C4" t="n">
-        <v>3584</v>
+        <v>8495</v>
       </c>
       <c r="D4" t="n">
-        <v>1911</v>
+        <v>3482</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1080</v>
+        <v>1033</v>
       </c>
       <c r="C5" t="n">
-        <v>2383</v>
+        <v>8496</v>
       </c>
       <c r="D5" t="n">
-        <v>1041</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="C6" t="n">
-        <v>997</v>
+        <v>4441</v>
       </c>
       <c r="D6" t="n">
-        <v>745</v>
+        <v>872</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>347</v>
+        <v>1111</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6653</v>
+        <v>2111</v>
       </c>
       <c r="C2" t="n">
-        <v>10355</v>
+        <v>16008</v>
       </c>
       <c r="D2" t="n">
-        <v>19383</v>
+        <v>34682</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4785</v>
+        <v>1712</v>
       </c>
       <c r="C3" t="n">
-        <v>6450</v>
+        <v>7104</v>
       </c>
       <c r="D3" t="n">
-        <v>6832</v>
+        <v>11392</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2337</v>
+        <v>1339</v>
       </c>
       <c r="C4" t="n">
-        <v>4941</v>
+        <v>7695</v>
       </c>
       <c r="D4" t="n">
-        <v>2570</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1385</v>
+        <v>1047</v>
       </c>
       <c r="C5" t="n">
-        <v>3025</v>
+        <v>8318</v>
       </c>
       <c r="D5" t="n">
-        <v>1184</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>689</v>
+        <v>603</v>
       </c>
       <c r="C6" t="n">
-        <v>1796</v>
+        <v>6069</v>
       </c>
       <c r="D6" t="n">
-        <v>783</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C7" t="n">
-        <v>722</v>
+        <v>2513</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>291</v>
+        <v>623</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4987</v>
+        <v>2038</v>
       </c>
       <c r="C2" t="n">
-        <v>12122</v>
+        <v>10629</v>
       </c>
       <c r="D2" t="n">
-        <v>24788</v>
+        <v>27905</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4699</v>
+        <v>2249</v>
       </c>
       <c r="C3" t="n">
-        <v>7447</v>
+        <v>12025</v>
       </c>
       <c r="D3" t="n">
-        <v>8348</v>
+        <v>12048</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3073</v>
+        <v>967</v>
       </c>
       <c r="C4" t="n">
-        <v>5707</v>
+        <v>12343</v>
       </c>
       <c r="D4" t="n">
-        <v>3285</v>
+        <v>3967</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1634</v>
+        <v>557</v>
       </c>
       <c r="C5" t="n">
-        <v>4028</v>
+        <v>5947</v>
       </c>
       <c r="D5" t="n">
-        <v>1414</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>951</v>
+        <v>209</v>
       </c>
       <c r="C6" t="n">
-        <v>2435</v>
+        <v>2462</v>
       </c>
       <c r="D6" t="n">
-        <v>845</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>407</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>1282</v>
+        <v>610</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>514</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
